--- a/theblock_perp_volume_since_2024.xlsx
+++ b/theblock_perp_volume_since_2024.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Perp Protocol Volume" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="HL vs Exchanges (Monthly)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="HL vs Binance (Monthly)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Total Futures Volumes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -555,10 +556,6 @@
       <c r="N2" t="n">
         <v>305349399</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -605,10 +602,6 @@
       <c r="N3" t="n">
         <v>178420345</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -655,10 +648,6 @@
       <c r="N4" t="n">
         <v>8705969318</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -705,10 +694,6 @@
       <c r="N5" t="n">
         <v>30173901532</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -755,10 +740,6 @@
       <c r="N6" t="n">
         <v>35214553262</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -805,10 +786,6 @@
       <c r="N7" t="n">
         <v>33011284772</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -855,10 +832,6 @@
       <c r="N8" t="n">
         <v>36925308201</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -905,11 +878,9 @@
       <c r="N9" t="n">
         <v>18414333833</v>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>870344790</v>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
         <v>23965726</v>
       </c>
@@ -959,11 +930,9 @@
       <c r="N10" t="n">
         <v>13609769273</v>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>1050289529</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
         <v>147489023</v>
       </c>
@@ -1013,11 +982,9 @@
       <c r="N11" t="n">
         <v>13501887553</v>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>3071381215</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
         <v>106911145</v>
       </c>
@@ -1067,11 +1034,9 @@
       <c r="N12" t="n">
         <v>26382680314</v>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
         <v>13564739577</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
         <v>265851528</v>
       </c>
@@ -1121,11 +1086,9 @@
       <c r="N13" t="n">
         <v>26650470343</v>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>8334023580</v>
       </c>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
         <v>282525303</v>
       </c>
@@ -1181,7 +1144,6 @@
       <c r="P14" t="n">
         <v>1426676774</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
         <v>290028874</v>
       </c>
@@ -1237,7 +1199,6 @@
       <c r="P15" t="n">
         <v>1133731632</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
         <v>181650190</v>
       </c>
@@ -1293,7 +1254,6 @@
       <c r="P16" t="n">
         <v>1515969698</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
         <v>92306853</v>
       </c>
@@ -1349,7 +1309,6 @@
       <c r="P17" t="n">
         <v>2602206250</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
         <v>94326800</v>
       </c>
@@ -1405,7 +1364,6 @@
       <c r="P18" t="n">
         <v>6596869705</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
         <v>270004912</v>
       </c>
@@ -1556,7 +1514,6 @@
       <c r="I21" t="n">
         <v>23733429723</v>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
         <v>14755446391</v>
       </c>
@@ -1612,7 +1569,6 @@
       <c r="I22" t="n">
         <v>17517945696</v>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
         <v>14595732811</v>
       </c>
@@ -1668,7 +1624,6 @@
       <c r="I23" t="n">
         <v>22139552463</v>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
         <v>75965561138</v>
       </c>
@@ -1724,7 +1679,6 @@
       <c r="I24" t="n">
         <v>7899164843</v>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
         <v>78360365127</v>
       </c>
@@ -1780,7 +1734,6 @@
       <c r="I25" t="n">
         <v>3088699131</v>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
         <v>70574031518</v>
       </c>
@@ -1836,7 +1789,6 @@
       <c r="I26" t="n">
         <v>2138852222</v>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="n">
         <v>37313952734</v>
       </c>
@@ -1892,7 +1844,6 @@
       <c r="I27" t="n">
         <v>1418823187</v>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
         <v>36331027258</v>
       </c>
@@ -1948,7 +1899,6 @@
       <c r="I28" t="n">
         <v>1143239794</v>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="n">
         <v>35530589630</v>
       </c>
@@ -2004,7 +1954,6 @@
       <c r="I29" t="n">
         <v>1607154108</v>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
         <v>34170001805</v>
       </c>
@@ -2060,7 +2009,6 @@
       <c r="I30" t="n">
         <v>1722251782</v>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
         <v>42333257637</v>
       </c>
@@ -2116,7 +2064,6 @@
       <c r="I31" t="n">
         <v>925401114</v>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="n">
         <v>23444916901</v>
       </c>
@@ -3177,4 +3124,1651 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ByBit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Huobi</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Gate.io</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>FTX</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>BitMEX</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Kucoin</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>crypto.com</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Deribit</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>dYdX V3</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Kraken</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Bitfinex</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Delta Exchange Global</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1507193377109.39</v>
+      </c>
+      <c r="C2" t="n">
+        <v>625038935502.595</v>
+      </c>
+      <c r="D2" t="n">
+        <v>462540308145.946</v>
+      </c>
+      <c r="E2" t="n">
+        <v>332070725882.897</v>
+      </c>
+      <c r="F2" t="n">
+        <v>23421233654.0245</v>
+      </c>
+      <c r="G2" t="n">
+        <v>62483177312.831</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>19905086777.0733</v>
+      </c>
+      <c r="J2" t="n">
+        <v>56720090714.4408</v>
+      </c>
+      <c r="K2" t="n">
+        <v>34236657066.5022</v>
+      </c>
+      <c r="L2" t="n">
+        <v>35429108427.3005</v>
+      </c>
+      <c r="M2" t="n">
+        <v>20749460586.11</v>
+      </c>
+      <c r="N2" t="n">
+        <v>11987420246.7411</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3021827816.47896</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2080819195.80237</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>9907864596.687639</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1534727797518.24</v>
+      </c>
+      <c r="C3" t="n">
+        <v>619499066608.277</v>
+      </c>
+      <c r="D3" t="n">
+        <v>491440177974.501</v>
+      </c>
+      <c r="E3" t="n">
+        <v>331729327930.255</v>
+      </c>
+      <c r="F3" t="n">
+        <v>23708862220.1557</v>
+      </c>
+      <c r="G3" t="n">
+        <v>65366051968.1907</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>16774749474.5465</v>
+      </c>
+      <c r="J3" t="n">
+        <v>57043151512.7229</v>
+      </c>
+      <c r="K3" t="n">
+        <v>33708196571.5199</v>
+      </c>
+      <c r="L3" t="n">
+        <v>34287297236.3863</v>
+      </c>
+      <c r="M3" t="n">
+        <v>13758814474.034</v>
+      </c>
+      <c r="N3" t="n">
+        <v>13952557877.1033</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2839939799.00127</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2393949127.15604</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>9110602809.58996</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2922514832211.77</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1157748422778.09</v>
+      </c>
+      <c r="D4" t="n">
+        <v>871402374150.1801</v>
+      </c>
+      <c r="E4" t="n">
+        <v>763410480665.89</v>
+      </c>
+      <c r="F4" t="n">
+        <v>43573152602.6578</v>
+      </c>
+      <c r="G4" t="n">
+        <v>121377514908.476</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>27937395010.0879</v>
+      </c>
+      <c r="J4" t="n">
+        <v>104444907173.295</v>
+      </c>
+      <c r="K4" t="n">
+        <v>44534716076.4218</v>
+      </c>
+      <c r="L4" t="n">
+        <v>61717797446.0639</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20308443753.7037</v>
+      </c>
+      <c r="N4" t="n">
+        <v>29896011648.1453</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5736691027.75247</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3989889779.47442</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>13710729740.7694</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2069126007255.19</v>
+      </c>
+      <c r="C5" t="n">
+        <v>868314905134.194</v>
+      </c>
+      <c r="D5" t="n">
+        <v>638389467240.85</v>
+      </c>
+      <c r="E5" t="n">
+        <v>645330031891.517</v>
+      </c>
+      <c r="F5" t="n">
+        <v>38901042896.5509</v>
+      </c>
+      <c r="G5" t="n">
+        <v>96237527444.4402</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>22959184825.3268</v>
+      </c>
+      <c r="J5" t="n">
+        <v>55461730925.7309</v>
+      </c>
+      <c r="K5" t="n">
+        <v>38489777279.7238</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39877460865.7411</v>
+      </c>
+      <c r="M5" t="n">
+        <v>14645437135.6052</v>
+      </c>
+      <c r="N5" t="n">
+        <v>29794166604.9533</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3516483137.87996</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2640072920.33262</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12048895057.1509</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1731976121318.75</v>
+      </c>
+      <c r="C6" t="n">
+        <v>747577722969.557</v>
+      </c>
+      <c r="D6" t="n">
+        <v>536052815122.529</v>
+      </c>
+      <c r="E6" t="n">
+        <v>499358260523.954</v>
+      </c>
+      <c r="F6" t="n">
+        <v>31366906781.8633</v>
+      </c>
+      <c r="G6" t="n">
+        <v>81780026084.1425</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>16872430720.1434</v>
+      </c>
+      <c r="J6" t="n">
+        <v>49220645119.5309</v>
+      </c>
+      <c r="K6" t="n">
+        <v>39873794642.8528</v>
+      </c>
+      <c r="L6" t="n">
+        <v>33437495722.6293</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10324981356.5841</v>
+      </c>
+      <c r="N6" t="n">
+        <v>35888091227.5237</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2327988805.14422</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2371120788.08825</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>10075873244.7737</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1380473678382.77</v>
+      </c>
+      <c r="C7" t="n">
+        <v>574045083551.236</v>
+      </c>
+      <c r="D7" t="n">
+        <v>689172451213.921</v>
+      </c>
+      <c r="E7" t="n">
+        <v>388160820700.059</v>
+      </c>
+      <c r="F7" t="n">
+        <v>42261828918.718</v>
+      </c>
+      <c r="G7" t="n">
+        <v>55362451001.128</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>21131944699.5089</v>
+      </c>
+      <c r="J7" t="n">
+        <v>57979599520.7394</v>
+      </c>
+      <c r="K7" t="n">
+        <v>60449479498.2603</v>
+      </c>
+      <c r="L7" t="n">
+        <v>31570822659.212</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9272215656.887791</v>
+      </c>
+      <c r="N7" t="n">
+        <v>27950095643.673</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2685012714.2212</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2694748861.89975</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7618635044.43193</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1556851182445.25</v>
+      </c>
+      <c r="C8" t="n">
+        <v>689924023189.519</v>
+      </c>
+      <c r="D8" t="n">
+        <v>768125093282.829</v>
+      </c>
+      <c r="E8" t="n">
+        <v>616458373996.833</v>
+      </c>
+      <c r="F8" t="n">
+        <v>43008051910.0093</v>
+      </c>
+      <c r="G8" t="n">
+        <v>84547845579.37309</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>22392184894.3063</v>
+      </c>
+      <c r="J8" t="n">
+        <v>62271884057.7079</v>
+      </c>
+      <c r="K8" t="n">
+        <v>95390557795.25369</v>
+      </c>
+      <c r="L8" t="n">
+        <v>35973908145.1154</v>
+      </c>
+      <c r="M8" t="n">
+        <v>8564721827.69409</v>
+      </c>
+      <c r="N8" t="n">
+        <v>25805087866.9974</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3067312412.14079</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2753670071.83154</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>10935483354.2328</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1591606079190.87</v>
+      </c>
+      <c r="C9" t="n">
+        <v>714104473166.928</v>
+      </c>
+      <c r="D9" t="n">
+        <v>639496405467.453</v>
+      </c>
+      <c r="E9" t="n">
+        <v>529877490640.719</v>
+      </c>
+      <c r="F9" t="n">
+        <v>34077850317.7744</v>
+      </c>
+      <c r="G9" t="n">
+        <v>69942962280.483</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>18180787828.5801</v>
+      </c>
+      <c r="J9" t="n">
+        <v>49889982145.0018</v>
+      </c>
+      <c r="K9" t="n">
+        <v>104498659381.721</v>
+      </c>
+      <c r="L9" t="n">
+        <v>31410134669.0928</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5256222636.55439</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20283750656.5896</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2863505417.4032</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4628425340.47095</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>10498885677.1915</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1279245290297.97</v>
+      </c>
+      <c r="C10" t="n">
+        <v>575884635166.822</v>
+      </c>
+      <c r="D10" t="n">
+        <v>512996517132.835</v>
+      </c>
+      <c r="E10" t="n">
+        <v>446667856411.489</v>
+      </c>
+      <c r="F10" t="n">
+        <v>26010560728.9325</v>
+      </c>
+      <c r="G10" t="n">
+        <v>64049916050.6282</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>11924714887.7522</v>
+      </c>
+      <c r="J10" t="n">
+        <v>37865994188.9084</v>
+      </c>
+      <c r="K10" t="n">
+        <v>149206936727.021</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18093595009.1575</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2524202826.09441</v>
+      </c>
+      <c r="N10" t="n">
+        <v>14129012583.209</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1851951136.32169</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1665154559.48022</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6336855726.3672</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1510476735275.23</v>
+      </c>
+      <c r="C11" t="n">
+        <v>662072306615.897</v>
+      </c>
+      <c r="D11" t="n">
+        <v>622040669983.249</v>
+      </c>
+      <c r="E11" t="n">
+        <v>566972658084.986</v>
+      </c>
+      <c r="F11" t="n">
+        <v>24858373675.8961</v>
+      </c>
+      <c r="G11" t="n">
+        <v>74297691876.3904</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>11876593375.7322</v>
+      </c>
+      <c r="J11" t="n">
+        <v>38961515783.9227</v>
+      </c>
+      <c r="K11" t="n">
+        <v>140624113696.343</v>
+      </c>
+      <c r="L11" t="n">
+        <v>21343918436.1236</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1323055163.7829</v>
+      </c>
+      <c r="N11" t="n">
+        <v>17268016418.8254</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2012723788.14884</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1232212689.2231</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7180770196.6344</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2986397427981.75</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1233827674267.04</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1176435640228.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1059316659223.09</v>
+      </c>
+      <c r="F12" t="n">
+        <v>54613673950.5601</v>
+      </c>
+      <c r="G12" t="n">
+        <v>129026663235.568</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>28095451652.881</v>
+      </c>
+      <c r="J12" t="n">
+        <v>78714218162.0162</v>
+      </c>
+      <c r="K12" t="n">
+        <v>190912635548.791</v>
+      </c>
+      <c r="L12" t="n">
+        <v>52020118549.8799</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>44080838478.9618</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5535038144.53325</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1211867247.37133</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3075027057349.76</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1217447697053.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1172413041710.15</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1050883457600.43</v>
+      </c>
+      <c r="F13" t="n">
+        <v>48691122381.2366</v>
+      </c>
+      <c r="G13" t="n">
+        <v>145424710552.689</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>31480730571.3486</v>
+      </c>
+      <c r="J13" t="n">
+        <v>80516321756.9745</v>
+      </c>
+      <c r="K13" t="n">
+        <v>208683731842.961</v>
+      </c>
+      <c r="L13" t="n">
+        <v>55045383467.6107</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>40905430375.2408</v>
+      </c>
+      <c r="O13" t="n">
+        <v>7118734814.02628</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1301188366.36254</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2499145552972.75</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1024619789880.92</v>
+      </c>
+      <c r="D14" t="n">
+        <v>904347473532.498</v>
+      </c>
+      <c r="E14" t="n">
+        <v>902792770976.525</v>
+      </c>
+      <c r="F14" t="n">
+        <v>44272432279.4343</v>
+      </c>
+      <c r="G14" t="n">
+        <v>143968246555.914</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>24594239371.5562</v>
+      </c>
+      <c r="J14" t="n">
+        <v>67341434339.9555</v>
+      </c>
+      <c r="K14" t="n">
+        <v>166262274842.585</v>
+      </c>
+      <c r="L14" t="n">
+        <v>46423433720.4691</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>33465345375.8682</v>
+      </c>
+      <c r="O14" t="n">
+        <v>7563384748.99839</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1186441767.07221</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5621324942.04413</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1986721182124.09</v>
+      </c>
+      <c r="C15" t="n">
+        <v>843865330335.484</v>
+      </c>
+      <c r="D15" t="n">
+        <v>682337425004.698</v>
+      </c>
+      <c r="E15" t="n">
+        <v>682109296890.95</v>
+      </c>
+      <c r="F15" t="n">
+        <v>37455402556.744</v>
+      </c>
+      <c r="G15" t="n">
+        <v>149226553434.038</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>20590900665.1952</v>
+      </c>
+      <c r="J15" t="n">
+        <v>49913619203.5582</v>
+      </c>
+      <c r="K15" t="n">
+        <v>118734212343.502</v>
+      </c>
+      <c r="L15" t="n">
+        <v>37590087504.7372</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>24636814667.2728</v>
+      </c>
+      <c r="O15" t="n">
+        <v>7144228211.89315</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1033518578.51136</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6410800729.29944</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1948120657288.15</v>
+      </c>
+      <c r="C16" t="n">
+        <v>861787543492.861</v>
+      </c>
+      <c r="D16" t="n">
+        <v>648218439462.261</v>
+      </c>
+      <c r="E16" t="n">
+        <v>656897332030.656</v>
+      </c>
+      <c r="F16" t="n">
+        <v>36000383926.3236</v>
+      </c>
+      <c r="G16" t="n">
+        <v>166112859471.662</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>18478826516.1548</v>
+      </c>
+      <c r="J16" t="n">
+        <v>51493753769.2597</v>
+      </c>
+      <c r="K16" t="n">
+        <v>76339350830.54401</v>
+      </c>
+      <c r="L16" t="n">
+        <v>36456702100.174</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>30161613648.9919</v>
+      </c>
+      <c r="O16" t="n">
+        <v>8227711547.25793</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1059815828.55899</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7218754336.5244</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1929216673131.09</v>
+      </c>
+      <c r="C17" t="n">
+        <v>887357133571.005</v>
+      </c>
+      <c r="D17" t="n">
+        <v>656850848215.401</v>
+      </c>
+      <c r="E17" t="n">
+        <v>665494199701.902</v>
+      </c>
+      <c r="F17" t="n">
+        <v>41222750334.2879</v>
+      </c>
+      <c r="G17" t="n">
+        <v>169680576710.63</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>18272907864.1898</v>
+      </c>
+      <c r="J17" t="n">
+        <v>57900224327.4939</v>
+      </c>
+      <c r="K17" t="n">
+        <v>64605620162.3153</v>
+      </c>
+      <c r="L17" t="n">
+        <v>29348831606.3709</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>26512994901.3165</v>
+      </c>
+      <c r="O17" t="n">
+        <v>6635312958.70187</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1075695646.83073</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6132856749.25456</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2363518330743.03</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1003912762710.97</v>
+      </c>
+      <c r="D18" t="n">
+        <v>793461692837.2729</v>
+      </c>
+      <c r="E18" t="n">
+        <v>799545786276.001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>58060793727.623</v>
+      </c>
+      <c r="G18" t="n">
+        <v>283245330607.854</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>19204407052.0196</v>
+      </c>
+      <c r="J18" t="n">
+        <v>61013836137.4589</v>
+      </c>
+      <c r="K18" t="n">
+        <v>64911776372.684</v>
+      </c>
+      <c r="L18" t="n">
+        <v>36283964636.0762</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>33713873041.9475</v>
+      </c>
+      <c r="O18" t="n">
+        <v>5321997320.58008</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1051423853.70299</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5268450764.19205</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1921878896649.96</v>
+      </c>
+      <c r="C19" t="n">
+        <v>842883668693.538</v>
+      </c>
+      <c r="D19" t="n">
+        <v>662165398262.428</v>
+      </c>
+      <c r="E19" t="n">
+        <v>665982794692.826</v>
+      </c>
+      <c r="F19" t="n">
+        <v>53733654664.2488</v>
+      </c>
+      <c r="G19" t="n">
+        <v>272227602999.023</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>15662525699.2959</v>
+      </c>
+      <c r="J19" t="n">
+        <v>52085643130.4792</v>
+      </c>
+      <c r="K19" t="n">
+        <v>44649257381.0384</v>
+      </c>
+      <c r="L19" t="n">
+        <v>29972254916.9604</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>29607506087.3867</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3818517821.75765</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1041819090.60686</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3824682746.69088</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2677722540542.34</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1103589660548.33</v>
+      </c>
+      <c r="D20" t="n">
+        <v>836391351085.189</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1043052236316.56</v>
+      </c>
+      <c r="F20" t="n">
+        <v>71441021721.99091</v>
+      </c>
+      <c r="G20" t="n">
+        <v>392369833474.207</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>20314798557.9209</v>
+      </c>
+      <c r="J20" t="n">
+        <v>88090311577.9704</v>
+      </c>
+      <c r="K20" t="n">
+        <v>66995510482.3788</v>
+      </c>
+      <c r="L20" t="n">
+        <v>44290975719.1161</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>43578251732.1817</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3768582055.05762</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1057446550.4244</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4657260736.01833</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2882680820909.69</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1233048220895.71</v>
+      </c>
+      <c r="D21" t="n">
+        <v>878122292073.958</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1079163408860.48</v>
+      </c>
+      <c r="F21" t="n">
+        <v>78865027890.0121</v>
+      </c>
+      <c r="G21" t="n">
+        <v>799442561673.7729</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>20285121658.2221</v>
+      </c>
+      <c r="J21" t="n">
+        <v>91786883769.51241</v>
+      </c>
+      <c r="K21" t="n">
+        <v>82045312151.6893</v>
+      </c>
+      <c r="L21" t="n">
+        <v>51064632005.5364</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>45658611912.1785</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4590773417.96453</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1151891816.92253</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4199745163.70276</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2342740999651.98</v>
+      </c>
+      <c r="C22" t="n">
+        <v>907611966153.85</v>
+      </c>
+      <c r="D22" t="n">
+        <v>638224719439.24</v>
+      </c>
+      <c r="E22" t="n">
+        <v>739175904232.905</v>
+      </c>
+      <c r="F22" t="n">
+        <v>50867871292.1834</v>
+      </c>
+      <c r="G22" t="n">
+        <v>712222613857.993</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>17095722720.3776</v>
+      </c>
+      <c r="J22" t="n">
+        <v>38244532630.5123</v>
+      </c>
+      <c r="K22" t="n">
+        <v>72479893952.6304</v>
+      </c>
+      <c r="L22" t="n">
+        <v>41129180779.5112</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>28136960205.1612</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1454915698.29276</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1036674102.30173</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2025176909.19586</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2922130264108.44</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1199554127971.15</v>
+      </c>
+      <c r="D23" t="n">
+        <v>836760283799.2679</v>
+      </c>
+      <c r="E23" t="n">
+        <v>715237632304.167</v>
+      </c>
+      <c r="F23" t="n">
+        <v>65472022421.0805</v>
+      </c>
+      <c r="G23" t="n">
+        <v>834675101876.4301</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>23237542836.178</v>
+      </c>
+      <c r="J23" t="n">
+        <v>108305773703.974</v>
+      </c>
+      <c r="K23" t="n">
+        <v>102328192612.788</v>
+      </c>
+      <c r="L23" t="n">
+        <v>68111256257.8097</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>36782999799.7683</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4601717487.10163</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1115338905.37893</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2617991906.19921</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2273092247607.43</v>
+      </c>
+      <c r="C24" t="n">
+        <v>945394935613.254</v>
+      </c>
+      <c r="D24" t="n">
+        <v>579452119677.359</v>
+      </c>
+      <c r="E24" t="n">
+        <v>350979009191.776</v>
+      </c>
+      <c r="F24" t="n">
+        <v>55662725616.9594</v>
+      </c>
+      <c r="G24" t="n">
+        <v>618827338996.1379</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>17690107081.8687</v>
+      </c>
+      <c r="J24" t="n">
+        <v>91160476561.1067</v>
+      </c>
+      <c r="K24" t="n">
+        <v>76228015317.6403</v>
+      </c>
+      <c r="L24" t="n">
+        <v>49680671094.886</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>26912534637.3921</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2895323105.56687</v>
+      </c>
+      <c r="P24" t="n">
+        <v>944831687.884902</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2358476762.91387</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1646208701890.68</v>
+      </c>
+      <c r="C25" t="n">
+        <v>726644713616.7629</v>
+      </c>
+      <c r="D25" t="n">
+        <v>475359516275.732</v>
+      </c>
+      <c r="E25" t="n">
+        <v>297989002111.653</v>
+      </c>
+      <c r="F25" t="n">
+        <v>51678821142.424</v>
+      </c>
+      <c r="G25" t="n">
+        <v>493790208327.57</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>12516596939.9568</v>
+      </c>
+      <c r="J25" t="n">
+        <v>55274764185.5263</v>
+      </c>
+      <c r="K25" t="n">
+        <v>51180661483.4733</v>
+      </c>
+      <c r="L25" t="n">
+        <v>34423621046.5035</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>24317451786.3279</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4199972958.58588</v>
+      </c>
+      <c r="P25" t="n">
+        <v>931943806.870971</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2426223540.2456</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1677739242903.99</v>
+      </c>
+      <c r="C26" t="n">
+        <v>748905796546.223</v>
+      </c>
+      <c r="D26" t="n">
+        <v>446450455300.643</v>
+      </c>
+      <c r="E26" t="n">
+        <v>310997495469.583</v>
+      </c>
+      <c r="F26" t="n">
+        <v>54446374435.3523</v>
+      </c>
+      <c r="G26" t="n">
+        <v>491992155773.404</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>11434802957.2847</v>
+      </c>
+      <c r="J26" t="n">
+        <v>50326257905.2635</v>
+      </c>
+      <c r="K26" t="n">
+        <v>54480303692.9035</v>
+      </c>
+      <c r="L26" t="n">
+        <v>31963486002.1618</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>20332914494.5667</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3783054182.56346</v>
+      </c>
+      <c r="P26" t="n">
+        <v>28327069024.098</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1970533562.29706</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1688425815618.03</v>
+      </c>
+      <c r="C27" t="n">
+        <v>757232533822.325</v>
+      </c>
+      <c r="D27" t="n">
+        <v>429219286552.334</v>
+      </c>
+      <c r="E27" t="n">
+        <v>288895095398.427</v>
+      </c>
+      <c r="F27" t="n">
+        <v>50382446430.7362</v>
+      </c>
+      <c r="G27" t="n">
+        <v>507272974876.426</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>10365965388.6004</v>
+      </c>
+      <c r="J27" t="n">
+        <v>54452515577.5771</v>
+      </c>
+      <c r="K27" t="n">
+        <v>45904084117.0948</v>
+      </c>
+      <c r="L27" t="n">
+        <v>37012371243.9815</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>24085400002.0453</v>
+      </c>
+      <c r="O27" t="n">
+        <v>6872626583.76239</v>
+      </c>
+      <c r="P27" t="n">
+        <v>860974065.700953</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2939423822.65486</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1597093055824.87</v>
+      </c>
+      <c r="C28" t="n">
+        <v>720417715934.056</v>
+      </c>
+      <c r="D28" t="n">
+        <v>415744211955.187</v>
+      </c>
+      <c r="E28" t="n">
+        <v>275786602189.455</v>
+      </c>
+      <c r="F28" t="n">
+        <v>43575084356.7084</v>
+      </c>
+      <c r="G28" t="n">
+        <v>486858877614.08</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>8532233694.75937</v>
+      </c>
+      <c r="J28" t="n">
+        <v>58745407503.7171</v>
+      </c>
+      <c r="K28" t="n">
+        <v>36056899057.1817</v>
+      </c>
+      <c r="L28" t="n">
+        <v>25218052502.6225</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>20264140630.8974</v>
+      </c>
+      <c r="O28" t="n">
+        <v>4590741219.37098</v>
+      </c>
+      <c r="P28" t="n">
+        <v>677490860.76609</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4229447196.88163</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1375966467165.67</v>
+      </c>
+      <c r="C29" t="n">
+        <v>622677151284.673</v>
+      </c>
+      <c r="D29" t="n">
+        <v>352039607080.507</v>
+      </c>
+      <c r="E29" t="n">
+        <v>242457571667.735</v>
+      </c>
+      <c r="F29" t="n">
+        <v>36483543448.6457</v>
+      </c>
+      <c r="G29" t="n">
+        <v>356349585920.566</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>7683156803.11515</v>
+      </c>
+      <c r="J29" t="n">
+        <v>43176573568.1052</v>
+      </c>
+      <c r="K29" t="n">
+        <v>24362906338.28</v>
+      </c>
+      <c r="L29" t="n">
+        <v>20433023826.7989</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>16803351518.4917</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2868194592.25254</v>
+      </c>
+      <c r="P29" t="n">
+        <v>436090512.78439</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3176469121.50322</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1386011292859.66</v>
+      </c>
+      <c r="C30" t="n">
+        <v>614285363124.072</v>
+      </c>
+      <c r="D30" t="n">
+        <v>301018600172.729</v>
+      </c>
+      <c r="E30" t="n">
+        <v>232105864499.462</v>
+      </c>
+      <c r="F30" t="n">
+        <v>39118881314.2287</v>
+      </c>
+      <c r="G30" t="n">
+        <v>336147490044.065</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>7658429661.80789</v>
+      </c>
+      <c r="J30" t="n">
+        <v>33824052413.3112</v>
+      </c>
+      <c r="K30" t="n">
+        <v>26984223320.5028</v>
+      </c>
+      <c r="L30" t="n">
+        <v>17258024303.8344</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>16934477567.9166</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3334004979.87914</v>
+      </c>
+      <c r="P30" t="n">
+        <v>123844673.6401</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1914132164.86606</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1030513523196.01</v>
+      </c>
+      <c r="C31" t="n">
+        <v>463288686983.097</v>
+      </c>
+      <c r="D31" t="n">
+        <v>223182505225.405</v>
+      </c>
+      <c r="E31" t="n">
+        <v>177299964790.874</v>
+      </c>
+      <c r="F31" t="n">
+        <v>18634056928.9831</v>
+      </c>
+      <c r="G31" t="n">
+        <v>238186460892.977</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>5252091826.96984</v>
+      </c>
+      <c r="J31" t="n">
+        <v>21962461388.8484</v>
+      </c>
+      <c r="K31" t="n">
+        <v>18283316888.9389</v>
+      </c>
+      <c r="L31" t="n">
+        <v>14502485414.4536</v>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>14763448608.8779</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2299091814.93722</v>
+      </c>
+      <c r="P31" t="n">
+        <v>97470041.5351</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2274707859.3543</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>